--- a/docentes/García Sánchez Magda Bexabe - Estadisticos 20221.xlsx
+++ b/docentes/García Sánchez Magda Bexabe - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -82,10 +82,7 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>TELE</t>
+    <t>ROSAS</t>
   </si>
   <si>
     <t>MARTINEZ</t>
@@ -97,10 +94,7 @@
     <t>CERON</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
+    <t>REYES</t>
   </si>
   <si>
     <t>PELLICO</t>
@@ -112,10 +106,7 @@
     <t>ORTEGA</t>
   </si>
   <si>
-    <t>JIMENA</t>
-  </si>
-  <si>
-    <t>BETSABETH</t>
+    <t>ESTEFANY VIANEY</t>
   </si>
   <si>
     <t>FLORENTINA ESMERALDA</t>
@@ -548,19 +539,19 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3">
         <v>26</v>
       </c>
       <c r="G3">
-        <v>83.87</v>
+        <v>86.67</v>
       </c>
       <c r="H3">
         <v>6.9</v>
@@ -652,7 +643,7 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -661,13 +652,13 @@
         <v>7</v>
       </c>
       <c r="F7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>83.33</v>
+        <v>83.72</v>
       </c>
       <c r="H7">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -740,13 +731,13 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -832,13 +823,13 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -920,19 +911,19 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3">
         <v>26</v>
       </c>
       <c r="G3">
-        <v>83.87</v>
+        <v>86.67</v>
       </c>
       <c r="H3">
         <v>6.9</v>
@@ -1024,7 +1015,7 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1033,13 +1024,13 @@
         <v>7</v>
       </c>
       <c r="F7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>83.33</v>
+        <v>83.72</v>
       </c>
       <c r="H7">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1049,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1081,22 +1072,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920068</v>
+        <v>22330051920142</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1104,62 +1095,62 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920121</v>
+        <v>22330051920348</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920348</v>
+        <v>22330051920292</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920292</v>
+        <v>22330051920157</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1168,29 +1159,6 @@
         <v>14</v>
       </c>
       <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920157</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6">
         <v>1</v>
       </c>
     </row>

--- a/docentes/García Sánchez Magda Bexabe - Estadisticos 20221.xlsx
+++ b/docentes/García Sánchez Magda Bexabe - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="30">
   <si>
     <t>Mat</t>
   </si>
@@ -82,37 +82,28 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ROSAS</t>
+    <t>RAMIREZ</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>BELLO</t>
-  </si>
-  <si>
     <t>CERON</t>
   </si>
   <si>
-    <t>REYES</t>
+    <t>LUNA</t>
   </si>
   <si>
     <t>PELLICO</t>
   </si>
   <si>
-    <t>MORALES</t>
-  </si>
-  <si>
     <t>ORTEGA</t>
   </si>
   <si>
-    <t>ESTEFANY VIANEY</t>
+    <t>GUSTAVO</t>
   </si>
   <si>
     <t>FLORENTINA ESMERALDA</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
   </si>
   <si>
     <t>JESUS EMMANUEL</t>
@@ -711,16 +702,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>94.12</v>
+      </c>
+      <c r="H2">
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -734,16 +728,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>86.67</v>
+      </c>
+      <c r="H3">
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -757,16 +754,19 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>87.5</v>
+      </c>
+      <c r="H4">
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -780,16 +780,19 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>95.45</v>
+      </c>
+      <c r="H5">
+        <v>8.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -803,16 +806,19 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>86.05</v>
+      </c>
+      <c r="H6">
+        <v>7.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -826,16 +832,19 @@
         <v>43</v>
       </c>
       <c r="D7">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>79.06999999999999</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -891,16 +900,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>88.23999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -926,7 +935,7 @@
         <v>86.67</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -943,16 +952,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G4">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -978,7 +987,7 @@
         <v>95.45</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1004,7 +1013,7 @@
         <v>86.05</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1021,16 +1030,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F7">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G7">
-        <v>83.72</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -1040,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1072,22 +1081,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920142</v>
+        <v>22330051920386</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1101,10 +1110,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1118,16 +1127,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920292</v>
+        <v>22330051920157</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1136,29 +1145,6 @@
         <v>14</v>
       </c>
       <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920157</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5">
         <v>1</v>
       </c>
     </row>

--- a/docentes/García Sánchez Magda Bexabe - Estadisticos 20221.xlsx
+++ b/docentes/García Sánchez Magda Bexabe - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="39">
   <si>
     <t>Mat</t>
   </si>
@@ -82,31 +82,58 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>CERON</t>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
   </si>
   <si>
     <t>LUNA</t>
   </si>
   <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
+    <t>JIMENA</t>
+  </si>
+  <si>
+    <t>DANA PAOLA</t>
+  </si>
+  <si>
+    <t>LUIS BRANDON</t>
+  </si>
+  <si>
+    <t>FLORENTINA ESMERALDA</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
   </si>
   <si>
     <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>FLORENTINA ESMERALDA</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
   </si>
 </sst>
 </file>
@@ -1049,7 +1076,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1081,22 +1108,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920386</v>
+        <v>22330051920068</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1104,39 +1131,39 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920348</v>
+        <v>22330051920071</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920157</v>
+        <v>22330051920161</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1145,6 +1172,75 @@
         <v>14</v>
       </c>
       <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>22330051920348</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>22330051920157</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>22330051920386</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/García Sánchez Magda Bexabe - Estadisticos 20221.xlsx
+++ b/docentes/García Sánchez Magda Bexabe - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="42">
   <si>
     <t>Mat</t>
   </si>
@@ -91,6 +91,9 @@
     <t>CONTRERAS</t>
   </si>
   <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
@@ -109,6 +112,9 @@
     <t>ANTONIO</t>
   </si>
   <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
     <t>PELLICO</t>
   </si>
   <si>
@@ -125,6 +131,9 @@
   </si>
   <si>
     <t>LUIS BRANDON</t>
+  </si>
+  <si>
+    <t>MARIO</t>
   </si>
   <si>
     <t>FLORENTINA ESMERALDA</t>
@@ -1076,7 +1085,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1114,10 +1123,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1137,10 +1146,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1160,10 +1169,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1177,45 +1186,45 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920348</v>
+        <v>22330051920296</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920157</v>
+        <v>22330051920348</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1223,16 +1232,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920386</v>
+        <v>22330051920157</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1241,6 +1250,29 @@
         <v>14</v>
       </c>
       <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920386</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8">
         <v>1</v>
       </c>
     </row>

--- a/docentes/García Sánchez Magda Bexabe - Estadisticos 20221.xlsx
+++ b/docentes/García Sánchez Magda Bexabe - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="48">
   <si>
     <t>Mat</t>
   </si>
@@ -88,6 +88,12 @@
     <t>MENDOZA</t>
   </si>
   <si>
+    <t>GAMBOA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
     <t>CONTRERAS</t>
   </si>
   <si>
@@ -109,6 +115,12 @@
     <t>GUTIERREZ</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>VIDERIQUE</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
@@ -128,6 +140,12 @@
   </si>
   <si>
     <t>DANA PAOLA</t>
+  </si>
+  <si>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
+    <t>BELEN</t>
   </si>
   <si>
     <t>LUIS BRANDON</t>
@@ -971,7 +989,7 @@
         <v>86.67</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1085,7 +1103,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1123,10 +1141,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1146,10 +1164,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1163,22 +1181,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920161</v>
+        <v>22330051920091</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1186,22 +1204,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920296</v>
+        <v>22330051920141</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1209,39 +1227,39 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920348</v>
+        <v>22330051920161</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920157</v>
+        <v>22330051920296</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1250,29 +1268,75 @@
         <v>14</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920386</v>
+        <v>22330051920348</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920157</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
         <v>14</v>
       </c>
-      <c r="G8">
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920386</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/García Sánchez Magda Bexabe - Estadisticos 20221.xlsx
+++ b/docentes/García Sánchez Magda Bexabe - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="30">
   <si>
     <t>Mat</t>
   </si>
@@ -85,82 +85,28 @@
     <t>MACHORRO</t>
   </si>
   <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>GAMBOA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
+    <t>LUNA</t>
   </si>
   <si>
     <t>COYOHUA</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>VIDERIQUE</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
+    <t>VAZQUEZ</t>
   </si>
   <si>
     <t>TEZOCO</t>
   </si>
   <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
     <t>JIMENA</t>
   </si>
   <si>
-    <t>DANA PAOLA</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>BELEN</t>
-  </si>
-  <si>
-    <t>LUIS BRANDON</t>
+    <t>KAREN</t>
   </si>
   <si>
     <t>MARIO</t>
-  </si>
-  <si>
-    <t>FLORENTINA ESMERALDA</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
   </si>
 </sst>
 </file>
@@ -1015,7 +961,7 @@
         <v>87.5</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1058,16 +1004,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G6">
-        <v>86.05</v>
+        <v>88.37</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1084,16 +1030,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G7">
-        <v>79.06999999999999</v>
+        <v>86.05</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -1103,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1141,10 +1087,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1158,22 +1104,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920071</v>
+        <v>22330051920247</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1181,163 +1127,25 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920091</v>
+        <v>22330051920296</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G4">
         <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920141</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920161</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920296</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920348</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920157</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920386</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
